--- a/BS_Scenarios/scenario_analysis_template.xlsx
+++ b/BS_Scenarios/scenario_analysis_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yushi/Documents/GitHub/Yushi-Wei/BS_Scenarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5B9DFE-924D-F846-8771-7ED58DB52336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC31CFA8-9C82-9041-A30C-F91331F5C787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="15720" xr2:uid="{FA7A72B3-722C-4F6C-A60C-EF1A6BAD9396}"/>
   </bookViews>
@@ -74,10 +74,10 @@
     <t>Skew is defined as the 90% put - 115% call, when skew steepens, keep the ATM vol the same</t>
   </si>
   <si>
-    <t>ATM vol ranging from 15% to 25% in 1% increments</t>
-  </si>
-  <si>
     <t>Skew going from 5% to 15% in 1% increment</t>
+  </si>
+  <si>
+    <t>Vol parallel shift ranging from 15% to 25% in 1% increments</t>
   </si>
 </sst>
 </file>
@@ -496,7 +496,7 @@
         <v>0.03</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -507,7 +507,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
